--- a/KIF Training Log.xlsx
+++ b/KIF Training Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Kolding-Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3311735F-A44C-4A24-BF04-0EA63B45C7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54573181-27DD-432A-8886-4BC51E05F5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3BBAEB4D-ADBD-3543-8E36-8ADB13F8F78A}"/>
   </bookViews>

--- a/KIF Training Log.xlsx
+++ b/KIF Training Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Kolding-Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54573181-27DD-432A-8886-4BC51E05F5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0FD0093-9FD2-4268-B8D3-1D28C66BF302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3BBAEB4D-ADBD-3543-8E36-8ADB13F8F78A}"/>
   </bookViews>
@@ -1116,7 +1116,7 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="7">
         <v>46059</v>

--- a/KIF Training Log.xlsx
+++ b/KIF Training Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Kolding-Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0FD0093-9FD2-4268-B8D3-1D28C66BF302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4659723D-1144-49F0-9632-F5883C4EB9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3BBAEB4D-ADBD-3543-8E36-8ADB13F8F78A}"/>
   </bookViews>
@@ -111,9 +111,6 @@
     <t>Offensive roles</t>
   </si>
   <si>
-    <t>Defenisve roles</t>
-  </si>
-  <si>
     <t>Def 1</t>
   </si>
   <si>
@@ -223,6 +220,9 @@
   </si>
   <si>
     <t>Set Piece</t>
+  </si>
+  <si>
+    <t>Defensive roles</t>
   </si>
 </sst>
 </file>
@@ -772,7 +772,7 @@
         <v>24</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>10</v>
@@ -790,7 +790,7 @@
         <v>14</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S1" s="6" t="s">
         <v>16</v>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W1" s="6" t="s">
         <v>18</v>
@@ -811,7 +811,7 @@
         <v>19</v>
       </c>
       <c r="Y1" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.4">
@@ -837,7 +837,7 @@
         <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
@@ -846,25 +846,25 @@
         <v>23</v>
       </c>
       <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
         <v>27</v>
       </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>28</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>29</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>30</v>
       </c>
-      <c r="P2" t="s">
-        <v>31</v>
-      </c>
       <c r="Q2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -883,10 +883,10 @@
         <v>18</v>
       </c>
       <c r="X2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Y2" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.4">
@@ -912,7 +912,7 @@
         <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I3" t="s">
         <v>22</v>
@@ -921,25 +921,25 @@
         <v>23</v>
       </c>
       <c r="K3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
         <v>32</v>
       </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>33</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>34</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>35</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>36</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>37</v>
       </c>
       <c r="R3">
         <v>2</v>
@@ -958,10 +958,10 @@
         <v>17</v>
       </c>
       <c r="X3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Y3" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.4">
@@ -987,7 +987,7 @@
         <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I4" t="s">
         <v>22</v>
@@ -996,25 +996,25 @@
         <v>23</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" t="s">
         <v>42</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>43</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" t="s">
         <v>44</v>
       </c>
-      <c r="O4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P4" t="s">
-        <v>45</v>
-      </c>
       <c r="Q4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R4">
         <v>0.5</v>
@@ -1033,10 +1033,10 @@
         <v>15</v>
       </c>
       <c r="X4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.4">
@@ -1062,34 +1062,34 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I5" t="s">
         <v>22</v>
       </c>
       <c r="J5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" t="s">
         <v>53</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>54</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>55</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>56</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>57</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>58</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>59</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>60</v>
       </c>
       <c r="R5">
         <v>0.5</v>
@@ -1108,10 +1108,10 @@
         <v>8.5</v>
       </c>
       <c r="X5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Y5" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.4">
@@ -1137,34 +1137,34 @@
         <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I6" t="s">
         <v>22</v>
       </c>
       <c r="J6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N6" t="s">
+        <v>60</v>
+      </c>
+      <c r="O6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P6" t="s">
         <v>61</v>
       </c>
-      <c r="O6" t="s">
-        <v>35</v>
-      </c>
-      <c r="P6" t="s">
-        <v>62</v>
-      </c>
       <c r="Q6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R6">
         <v>0.75</v>
@@ -1183,10 +1183,10 @@
         <v>10</v>
       </c>
       <c r="X6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Y6" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/KIF Training Log.xlsx
+++ b/KIF Training Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Kolding-Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4659723D-1144-49F0-9632-F5883C4EB9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5793656C-D062-470B-9825-4469A3D525D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3BBAEB4D-ADBD-3543-8E36-8ADB13F8F78A}"/>
   </bookViews>

--- a/KIF Training Log.xlsx
+++ b/KIF Training Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Kolding-Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5793656C-D062-470B-9825-4469A3D525D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04974EA6-604A-4108-BC99-6840C5F36D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3BBAEB4D-ADBD-3543-8E36-8ADB13F8F78A}"/>
   </bookViews>

--- a/KIF Training Log.xlsx
+++ b/KIF Training Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Kolding-Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04974EA6-604A-4108-BC99-6840C5F36D24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D6E6BB-A3F2-4C37-BB29-22AD91324A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3BBAEB4D-ADBD-3543-8E36-8ADB13F8F78A}"/>
   </bookViews>
@@ -738,462 +738,462 @@
   <sheetFormatPr defaultColWidth="20.83203125" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:25" ht="20" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="V1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="Y1" s="6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7">
+      <c r="A2" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7">
         <v>46058</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
       <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>21</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>38</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>26</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>25</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>27</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>28</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>29</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>37</v>
       </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
       <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
         <v>10</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <v>0.5</v>
       </c>
-      <c r="U2">
-        <f>(R2*S2)+(T2*(S2-1))</f>
+      <c r="V2">
+        <f>(S2*T2)+(U2*(T2-1))</f>
         <v>14.5</v>
       </c>
-      <c r="V2">
+      <c r="W2">
         <v>18</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>49</v>
-      </c>
-      <c r="Y2" s="8" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A3">
+      <c r="A3" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
+      <c r="C3" s="7">
         <v>46058</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>21</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>18</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>39</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>22</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>23</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>31</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>25</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>32</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>33</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>34</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>35</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>36</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>2</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>5</v>
       </c>
-      <c r="T3">
-        <v>1</v>
-      </c>
       <c r="U3">
-        <f t="shared" ref="U3:U5" si="0">(R3*S3)+(T3*(S3-1))</f>
+        <v>1</v>
+      </c>
+      <c r="V3">
+        <f t="shared" ref="V3:V5" si="0">(S3*T3)+(U3*(T3-1))</f>
         <v>14</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <v>17</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>49</v>
-      </c>
-      <c r="Y3" s="8" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A4">
+      <c r="A4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="B4" s="7">
+      <c r="C4" s="7">
         <v>46058</v>
       </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>21</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>18</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>40</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>22</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>23</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>26</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>41</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>42</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>43</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>29</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>44</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" t="s">
         <v>36</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>0.5</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>10</v>
       </c>
-      <c r="T4">
-        <v>1</v>
-      </c>
       <c r="U4">
+        <v>1</v>
+      </c>
+      <c r="V4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>15</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>49</v>
-      </c>
-      <c r="Y4" s="8" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A5">
+      <c r="A5" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="B5" s="7">
+      <c r="C5" s="7">
         <v>46059</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
       <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>2</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>20</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>21</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>18</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>51</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>22</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>52</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>53</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>54</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>55</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>56</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>57</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>58</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
         <v>59</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>0.5</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>5</v>
       </c>
-      <c r="T5">
-        <v>1</v>
-      </c>
       <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>8.5</v>
       </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
         <v>50</v>
-      </c>
-      <c r="Y5" s="8" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A6">
+      <c r="A6" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6">
         <v>6</v>
       </c>
-      <c r="B6" s="7">
+      <c r="C6" s="7">
         <v>46059</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
       <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>2</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>20</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>21</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>18</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>51</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>22</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>52</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>26</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>41</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N6" t="s">
         <v>32</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>60</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>34</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>61</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="R6" t="s">
         <v>37</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>0.75</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>8</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>0.5</v>
       </c>
-      <c r="U6">
-        <f t="shared" ref="U6" si="1">(R6*S6)+(T6*(S6-1))</f>
+      <c r="V6">
+        <f t="shared" ref="V6" si="1">(S6*T6)+(U6*(T6-1))</f>
         <v>9.5</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>10</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Y6" t="s">
         <v>50</v>
-      </c>
-      <c r="Y6" s="8" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="Y2" r:id="rId1" xr:uid="{CF420BEA-53D8-4EA7-BEDC-5E39C9A881DD}"/>
-    <hyperlink ref="Y3:Y5" r:id="rId2" display="www.kolding-if.dk" xr:uid="{2B65C98F-F34E-4AAE-AA33-F07EE41C674F}"/>
-    <hyperlink ref="Y6" r:id="rId3" xr:uid="{5EFBD91C-E07B-4E62-B0D9-9211CB750710}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{CF420BEA-53D8-4EA7-BEDC-5E39C9A881DD}"/>
+    <hyperlink ref="A3:A5" r:id="rId2" display="www.kolding-if.dk" xr:uid="{2B65C98F-F34E-4AAE-AA33-F07EE41C674F}"/>
+    <hyperlink ref="A6" r:id="rId3" xr:uid="{5EFBD91C-E07B-4E62-B0D9-9211CB750710}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/KIF Training Log.xlsx
+++ b/KIF Training Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Kolding-Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D6E6BB-A3F2-4C37-BB29-22AD91324A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE86E36-70A6-4AE8-A76F-0A6CCE295649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3BBAEB4D-ADBD-3543-8E36-8ADB13F8F78A}"/>
   </bookViews>
@@ -738,462 +738,462 @@
   <sheetFormatPr defaultColWidth="20.83203125" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:25" ht="20" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="U1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="V1" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="W1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="X1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y1" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="S1" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="T1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="U1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="V1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="W1" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="X1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y1" s="6" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A2" s="8" t="s">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7">
+        <v>46058</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2">
+        <v>18</v>
+      </c>
+      <c r="H2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>10</v>
+      </c>
+      <c r="T2">
+        <v>0.5</v>
+      </c>
+      <c r="U2">
+        <f>(R2*S2)+(T2*(S2-1))</f>
+        <v>14.5</v>
+      </c>
+      <c r="V2">
+        <v>18</v>
+      </c>
+      <c r="X2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y2" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7">
-        <v>46058</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>30</v>
-      </c>
-      <c r="R2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-      <c r="T2">
-        <v>10</v>
-      </c>
-      <c r="U2">
-        <v>0.5</v>
-      </c>
-      <c r="V2">
-        <f>(S2*T2)+(U2*(T2-1))</f>
-        <v>14.5</v>
-      </c>
-      <c r="W2">
-        <v>18</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A3" s="8" t="s">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7">
+        <v>46058</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3">
+        <v>2</v>
+      </c>
+      <c r="S3">
+        <v>5</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U5" si="0">(R3*S3)+(T3*(S3-1))</f>
+        <v>14</v>
+      </c>
+      <c r="V3">
+        <v>17</v>
+      </c>
+      <c r="X3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y3" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="7">
-        <v>46058</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R3" t="s">
-        <v>36</v>
-      </c>
-      <c r="S3">
-        <v>2</v>
-      </c>
-      <c r="T3">
-        <v>5</v>
-      </c>
-      <c r="U3">
-        <v>1</v>
-      </c>
-      <c r="V3">
-        <f t="shared" ref="V3:V5" si="0">(S3*T3)+(U3*(T3-1))</f>
-        <v>14</v>
-      </c>
-      <c r="W3">
-        <v>17</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A4" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="C4" s="7">
+      <c r="B4" s="7">
         <v>46058</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4">
-        <v>1</v>
+      <c r="E4" t="s">
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
         <v>21</v>
       </c>
-      <c r="H4">
+      <c r="G4">
         <v>18</v>
       </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
       <c r="I4" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="J4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O4" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="P4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="Q4" t="s">
-        <v>44</v>
-      </c>
-      <c r="R4" t="s">
         <v>36</v>
       </c>
+      <c r="R4">
+        <v>0.5</v>
+      </c>
       <c r="S4">
-        <v>0.5</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>1</v>
-      </c>
-      <c r="V4">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="W4">
+      <c r="V4">
         <v>15</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="X4" t="s">
         <v>49</v>
+      </c>
+      <c r="Y4" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A5" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="C5" s="7">
+      <c r="B5" s="7">
         <v>46059</v>
       </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
       <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
         <v>2</v>
       </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
       <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
         <v>21</v>
       </c>
-      <c r="H5">
+      <c r="G5">
         <v>18</v>
       </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
       <c r="I5" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="J5" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="K5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q5" t="s">
-        <v>58</v>
-      </c>
-      <c r="R5" t="s">
         <v>59</v>
       </c>
+      <c r="R5">
+        <v>0.5</v>
+      </c>
       <c r="S5">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>1</v>
-      </c>
-      <c r="V5">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="W5">
+      <c r="V5">
         <v>8.5</v>
       </c>
-      <c r="Y5" t="s">
+      <c r="X5" t="s">
         <v>50</v>
+      </c>
+      <c r="Y5" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A6" s="8" t="s">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6" s="7">
+        <v>46059</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6">
+        <v>18</v>
+      </c>
+      <c r="H6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" t="s">
+        <v>60</v>
+      </c>
+      <c r="O6" t="s">
+        <v>34</v>
+      </c>
+      <c r="P6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R6">
+        <v>0.75</v>
+      </c>
+      <c r="S6">
+        <v>8</v>
+      </c>
+      <c r="T6">
+        <v>0.5</v>
+      </c>
+      <c r="U6">
+        <f t="shared" ref="U6" si="1">(R6*S6)+(T6*(S6-1))</f>
+        <v>9.5</v>
+      </c>
+      <c r="V6">
+        <v>10</v>
+      </c>
+      <c r="X6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y6" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6" s="7">
-        <v>46059</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6">
-        <v>18</v>
-      </c>
-      <c r="I6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" t="s">
-        <v>52</v>
-      </c>
-      <c r="L6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" t="s">
-        <v>41</v>
-      </c>
-      <c r="N6" t="s">
-        <v>32</v>
-      </c>
-      <c r="O6" t="s">
-        <v>60</v>
-      </c>
-      <c r="P6" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>61</v>
-      </c>
-      <c r="R6" t="s">
-        <v>37</v>
-      </c>
-      <c r="S6">
-        <v>0.75</v>
-      </c>
-      <c r="T6">
-        <v>8</v>
-      </c>
-      <c r="U6">
-        <v>0.5</v>
-      </c>
-      <c r="V6">
-        <f t="shared" ref="V6" si="1">(S6*T6)+(U6*(T6-1))</f>
-        <v>9.5</v>
-      </c>
-      <c r="W6">
-        <v>10</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{CF420BEA-53D8-4EA7-BEDC-5E39C9A881DD}"/>
-    <hyperlink ref="A3:A5" r:id="rId2" display="www.kolding-if.dk" xr:uid="{2B65C98F-F34E-4AAE-AA33-F07EE41C674F}"/>
-    <hyperlink ref="A6" r:id="rId3" xr:uid="{5EFBD91C-E07B-4E62-B0D9-9211CB750710}"/>
+    <hyperlink ref="Y2" r:id="rId1" xr:uid="{CF420BEA-53D8-4EA7-BEDC-5E39C9A881DD}"/>
+    <hyperlink ref="Y3:Y5" r:id="rId2" display="www.kolding-if.dk" xr:uid="{2B65C98F-F34E-4AAE-AA33-F07EE41C674F}"/>
+    <hyperlink ref="Y6" r:id="rId3" xr:uid="{5EFBD91C-E07B-4E62-B0D9-9211CB750710}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/KIF Training Log.xlsx
+++ b/KIF Training Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Kolding-Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE86E36-70A6-4AE8-A76F-0A6CCE295649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F6A9FE-912F-48F9-BECE-52C385E6DAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3BBAEB4D-ADBD-3543-8E36-8ADB13F8F78A}"/>
   </bookViews>

--- a/KIF Training Log.xlsx
+++ b/KIF Training Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ben\Documents\GitHub\Kolding-Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F6A9FE-912F-48F9-BECE-52C385E6DAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A648AFB7-24F3-437B-8B4F-74FE188BDE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{3BBAEB4D-ADBD-3543-8E36-8ADB13F8F78A}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="63">
   <si>
     <t>Nº Drill</t>
   </si>
@@ -102,9 +102,6 @@
     <t>Winter Preseason</t>
   </si>
   <si>
-    <t>xx</t>
-  </si>
-  <si>
     <t>Monday</t>
   </si>
   <si>
@@ -223,6 +220,9 @@
   </si>
   <si>
     <t>Defensive roles</t>
+  </si>
+  <si>
+    <t>-4 Strenght</t>
   </si>
 </sst>
 </file>
@@ -374,7 +374,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -399,6 +399,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -769,10 +770,10 @@
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>10</v>
@@ -790,7 +791,7 @@
         <v>14</v>
       </c>
       <c r="R1" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S1" s="6" t="s">
         <v>16</v>
@@ -802,7 +803,7 @@
         <v>15</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W1" s="6" t="s">
         <v>18</v>
@@ -811,7 +812,7 @@
         <v>19</v>
       </c>
       <c r="Y1" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.4">
@@ -837,34 +838,34 @@
         <v>18</v>
       </c>
       <c r="H2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" t="s">
-        <v>23</v>
-      </c>
       <c r="K2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
         <v>26</v>
       </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>27</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>28</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>29</v>
       </c>
-      <c r="P2" t="s">
-        <v>30</v>
-      </c>
       <c r="Q2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R2">
         <v>1</v>
@@ -883,10 +884,10 @@
         <v>18</v>
       </c>
       <c r="X2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Y2" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.4">
@@ -912,34 +913,34 @@
         <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" t="s">
         <v>22</v>
       </c>
-      <c r="J3" t="s">
-        <v>23</v>
-      </c>
       <c r="K3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" t="s">
         <v>31</v>
       </c>
-      <c r="L3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>32</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>33</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>34</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>35</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>36</v>
       </c>
       <c r="R3">
         <v>2</v>
@@ -958,10 +959,10 @@
         <v>17</v>
       </c>
       <c r="X3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Y3" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.4">
@@ -987,34 +988,34 @@
         <v>18</v>
       </c>
       <c r="H4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
         <v>40</v>
       </c>
-      <c r="I4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>41</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>42</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" t="s">
         <v>43</v>
       </c>
-      <c r="O4" t="s">
-        <v>29</v>
-      </c>
-      <c r="P4" t="s">
-        <v>44</v>
-      </c>
       <c r="Q4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R4">
         <v>0.5</v>
@@ -1033,10 +1034,10 @@
         <v>15</v>
       </c>
       <c r="X4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Y4" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.4">
@@ -1062,34 +1063,34 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5">
+        <v>-3</v>
+      </c>
+      <c r="J5" t="s">
         <v>51</v>
       </c>
-      <c r="I5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>52</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>53</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>54</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>55</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>56</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>57</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>58</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>59</v>
       </c>
       <c r="R5">
         <v>0.5</v>
@@ -1108,10 +1109,10 @@
         <v>8.5</v>
       </c>
       <c r="X5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Y5" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.4">
@@ -1137,34 +1138,34 @@
         <v>18</v>
       </c>
       <c r="H6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6">
+        <v>-3</v>
+      </c>
+      <c r="J6" t="s">
         <v>51</v>
       </c>
-      <c r="I6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" t="s">
-        <v>52</v>
-      </c>
       <c r="K6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O6" t="s">
+        <v>33</v>
+      </c>
+      <c r="P6" t="s">
         <v>60</v>
       </c>
-      <c r="O6" t="s">
-        <v>34</v>
-      </c>
-      <c r="P6" t="s">
-        <v>61</v>
-      </c>
       <c r="Q6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R6">
         <v>0.75</v>
@@ -1183,10 +1184,10 @@
         <v>10</v>
       </c>
       <c r="X6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Y6" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
